--- a/Employee_Reports_wi48/Edilberto Angsioco Q0170.xlsx
+++ b/Employee_Reports_wi48/Edilberto Angsioco Q0170.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1758,237 +1758,237 @@
       <c r="K27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-018</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>18-Mar-2025</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>18-Mar-2026</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2027</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>21-May-2027</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-041</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>10-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>10-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Replacement Procedure Of Y Axis Frequency Inverter -Stacker Crane (SOPs)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>03-May-2025</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>03-May-2026</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-74</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-041</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-003</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>04-Apr-2025</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>04-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Replacement Procedure Of Y Axis Frequency Inverter -Stacker Crane (SOPs)</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>03-May-2025</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>03-May-2026</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>-71</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Stacker Crane Aisle Annual Maintenance And Megger Test Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-003</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>29-Jul-2025</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>29-Jul-2026</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="H32" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-011</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>31-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>31-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
+          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-018</t>
+          <t>LSME-CRG-SOP-011</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2025,11 +2025,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2045,28 +2045,40 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
+          <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-018</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2025</t>
+          <t>31-Aug-2025</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2026</t>
+          <t>31-Aug-2026</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2082,40 +2094,28 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Equipment Teaching Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-027</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>09-Jan-2026</t>
+          <t>24-Nov-2025</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>09-Jan-2027</t>
+          <t>24-Nov-2026</t>
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2131,36 +2131,85 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t>Equipment Teaching Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-027</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>09-Jan-2026</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>09-Jan-2027</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>04-Oct-2024</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>04-Oct-2026</t>
         </is>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2760,7 +2809,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2789,7 +2838,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2818,7 +2867,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2847,7 +2896,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2876,7 +2925,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2971,7 +3020,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3000,7 +3049,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3029,7 +3078,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7957</v>
+        <v>7954</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3058,7 +3107,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3087,7 +3136,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3116,7 +3165,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3194,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7957</v>
+        <v>7954</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3174,7 +3223,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3203,7 +3252,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3232,7 +3281,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7950</v>
+        <v>7947</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3261,7 +3310,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3290,7 +3339,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3319,7 +3368,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7950</v>
+        <v>7947</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3348,7 +3397,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
